--- a/vizualizare_date/cadre.xlsx
+++ b/vizualizare_date/cadre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VadimPK\Desktop\examsch\exam_app\vizualizare_date\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDE1B46-477B-4D76-A1AD-37EEAD714F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6782C08-9D19-460A-9CF8-2648E9868FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12870" yWindow="1905" windowWidth="13980" windowHeight="11115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4410" yWindow="975" windowWidth="13980" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4145" uniqueCount="2331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4145" uniqueCount="2329">
   <si>
     <t>id</t>
   </si>
@@ -7006,12 +7006,6 @@
   </si>
   <si>
     <t>Test</t>
-  </si>
-  <si>
-    <t>FIESC</t>
-  </si>
-  <si>
-    <t>SIC</t>
   </si>
   <si>
     <t>gheorghe.carare1@student.usv.ro</t>
@@ -21252,16 +21246,16 @@
         <v>2327</v>
       </c>
       <c r="D713" s="2" t="s">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="E713">
         <v>13123</v>
       </c>
       <c r="F713" t="s">
-        <v>2328</v>
+        <v>91</v>
       </c>
       <c r="G713" t="s">
-        <v>2329</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
